--- a/test.xlsx
+++ b/test.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lko99\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lko99\OneDrive\바탕 화면\깃허브_n8n\Execel_Data_Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72AD63D7-FB58-448A-8D9B-EE6A962445DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E172FCE-F5AF-4A12-9D6F-B470E5BD21EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="150" yWindow="630" windowWidth="21465" windowHeight="14835" xr2:uid="{2C4D6EA1-113F-441C-8DB3-5F4D9DA7E3F8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t>ID</t>
   </si>
@@ -81,6 +81,18 @@
   </si>
   <si>
     <t>최지은</t>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>결측치 있음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -479,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ACE6126-D3AB-4EC9-A968-731EB5606040}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="16.125" customWidth="1"/>
@@ -529,7 +541,7 @@
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -573,7 +585,7 @@
       </c>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -612,6 +624,37 @@
         <v>90</v>
       </c>
       <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2">
+        <v>23</v>
+      </c>
+      <c r="F7" s="2">
+        <v>98</v>
+      </c>
+      <c r="G7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2">
+        <v>21</v>
+      </c>
+      <c r="G8" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
